--- a/output/pdf_financials_xlsx/CRI.xlsx
+++ b/output/pdf_financials_xlsx/CRI.xlsx
@@ -3902,19 +3902,19 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.038946</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.683886</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.695743</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.891782</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.891782</v>
       </c>
     </row>
     <row r="93">
@@ -6391,7 +6391,11 @@
           <t>Warrants reserve 5</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -7103,7 +7107,11 @@
           <t>Warrants reserve 7</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -7591,7 +7599,11 @@
           <t>Warrants reserve 6</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -8494,7 +8506,11 @@
           <t>Warrants reserve 8</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CRI.xlsx
+++ b/output/pdf_financials_xlsx/CRI.xlsx
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000605</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0.000459</v>
@@ -1509,7 +1509,7 @@
         <v>-3.915903</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-3.915903</v>
+        <v>-3.916508</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-4.877225</v>
@@ -1589,7 +1589,7 @@
         <v>-3.911668</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.899985</v>
+        <v>-3.90059</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-4.861162</v>
@@ -1767,28 +1767,28 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.674278</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.575081</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000154</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.715709</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.163381</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.050827</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.976863</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.646083</v>
       </c>
     </row>
     <row r="35">
@@ -1839,28 +1839,28 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.674278</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.575081</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000154</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.715709</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.163381</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.050827</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.976863</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.646083</v>
       </c>
     </row>
     <row r="37">
@@ -2271,28 +2271,28 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.675028</v>
+        <v>0.00075</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.575831</v>
+        <v>0.00075</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.000664</v>
+        <v>0.00051</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.74157</v>
+        <v>0.025861</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.199346</v>
+        <v>0.035965</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.083521</v>
+        <v>0.032694</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.764374</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.687015</v>
+        <v>0.040932</v>
       </c>
     </row>
     <row r="49">
@@ -5030,13 +5030,13 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0045</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.01812</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0186</v>
       </c>
       <c r="H124" s="3" t="n">
         <v>0</v>
@@ -5066,13 +5066,13 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0045</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.01812</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0186</v>
       </c>
       <c r="H125" s="3" t="n">
         <v>0</v>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5850,7 +5850,11 @@
           <t>Reclamation deposits 3</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -6737,7 +6741,11 @@
           <t>Reclamation deposits 4</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -7841,7 +7849,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -9057,7 +9069,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -10377,7 +10389,11 @@
           <t>Cash paid for reclamation deposits 3</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -11662,7 +11678,11 @@
           <t>Cash paid for reclamation deposits 4</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -12654,7 +12674,11 @@
           <t>Cash paid for reclamation deposits</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -12713,7 +12737,11 @@
           <t>Lease payments 5</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -13988,7 +14016,11 @@
           <t>Cash paid for reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -14110,7 +14142,11 @@
           <t>Lease payments 7</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CRI.xlsx
+++ b/output/pdf_financials_xlsx/CRI.xlsx
@@ -3083,13 +3083,13 @@
         <v>0</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.013812</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.016076</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.01367</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0</v>
@@ -3119,13 +3119,13 @@
         <v>0</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0.047908</v>
+        <v>0.06172</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.016076</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.01367</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>0</v>
@@ -3261,13 +3261,13 @@
         <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.015902</v>
+        <v>0.00209</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.516076</v>
+        <v>0.5</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.098097</v>
+        <v>0.084427</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>0</v>
@@ -3449,17 +3449,13 @@
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.06072559403543552</v>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07823293946453787</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.005590847091931805</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.0048397106936364</v>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
@@ -4563,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000825</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -5411,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000825</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -5447,7 +5443,7 @@
         <v>-0.051262</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.234336</v>
+        <v>-1.235161</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-5.053975</v>
@@ -8158,7 +8154,11 @@
           <t>Current portion of lease obligation 7</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -13955,7 +13955,11 @@
           <t>Purchase of equipment 5</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
